--- a/jpcore-r4b/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
@@ -266,8 +266,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Extension.id</t>
@@ -280,10 +280,10 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -315,8 +315,8 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Extension.extension:structure</t>
@@ -347,13 +347,13 @@
 </t>
   </si>
   <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+    <t>拡張機能の意味を識別します / identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>拡張コードの定義のソース - 論理名またはURL。 / Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>定義は、拡張性コードの計算可能または人間が読み取る可能性のある定義を直接指している場合があります。または、他の仕様で宣言されているように、論理的なURIである場合があります。定義は、拡張機能を定義する構造定義のURIでなければなりません。 / The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -372,16 +372,16 @@
 </t>
   </si>
   <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4B/extensibility.html) for a list).</t>
+    <t>拡張値の値 / Value of extension</t>
+  </si>
+  <si>
+    <t>拡張値の値 - データ型の制約付きセットの1つでなければなりません（リストの[拡張性]（拡張性]（拡張性。html）を参照）。 / Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4B/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -419,13 +419,13 @@
 user content</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Extension.extension:bodyLandmarkOrientation.extension:landmarkDescription</t>
